--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-5.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9453EC36-541C-478A-9EDA-FBF4434C7D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3844A81B-E00D-469F-8D3A-694085087A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{58343094-920C-4EA4-A97F-1F68F1E1C53E}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{B132AE79-ADBE-4828-90A1-552A7992E06E}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="151" r:id="rId3"/>
+    <pivotCache cacheId="183" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576901736109" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{7DC1D269-C974-4802-9914-9FC7D3F2E3C4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579472800928" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{15C328C6-0B57-4EFB-88D8-46A1DACD5E95}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C68758D-C14C-467C-B9B2-800C56837A5F}" name="AllErrorPivot" cacheId="151" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{126B572F-9F89-4EC3-A773-7BAE1DD8AD2D}" name="AllErrorPivot" cacheId="183" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -579,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D66FE65-7DCA-4C95-B413-41C55580E24A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80AE8506-E579-4816-9B36-81FAC822DF58}">
   <dimension ref="A4:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -649,7 +649,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA5C1289-0CDA-4210-B363-AAC7FA1C7C8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B609676-A8BA-4BF4-BB14-F8EEE6FD368C}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
